--- a/data/trans_dic/IP11C$nada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria</t>
+          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,37</t>
+          <t>0,0; 68,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,85</t>
+          <t>0,0; 81,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,37 +737,37 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 38,37</t>
+          <t>3,56; 36,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,15</t>
+          <t>0,0; 39,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,81; 38,19</t>
+          <t>6,6; 37,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,47; 55,03</t>
+          <t>21,18; 54,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,19; 53,96</t>
+          <t>28,54; 55,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,65</t>
+          <t>0,0; 20,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,9</t>
+          <t>0,0; 42,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 20,95</t>
+          <t>3,49; 21,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,8; 34,12</t>
+          <t>13,82; 33,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 26,39</t>
+          <t>6,48; 27,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,14</t>
+          <t>0,0; 24,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,68; 29,8</t>
+          <t>12,34; 29,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,4; 40,28</t>
+          <t>23,51; 40,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 19,35</t>
+          <t>4,38; 19,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 25,05</t>
+          <t>2,77; 21,77</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,21</t>
+          <t>0,0; 40,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,17; 69,62</t>
+          <t>15,23; 67,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,23; 82,04</t>
+          <t>21,09; 81,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,13; 61,15</t>
+          <t>22,2; 62,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 60,63</t>
+          <t>8,94; 67,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 47,66</t>
+          <t>12,85; 48,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,92; 57,8</t>
+          <t>25,3; 58,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,9</t>
+          <t>5,42; 40,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,2; 40,43</t>
+          <t>16,7; 40,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,63; 52,6</t>
+          <t>29,18; 51,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 31,92</t>
+          <t>3,8; 35,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 25,43</t>
+          <t>8,31; 26,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,87; 34,51</t>
+          <t>17,87; 34,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 26,39</t>
+          <t>8,11; 28,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,13</t>
+          <t>0,0; 14,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,38; 28,35</t>
+          <t>14,11; 29,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,12; 38,15</t>
+          <t>25,25; 38,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 19,41</t>
+          <t>5,7; 18,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 16,92</t>
+          <t>1,9; 17,67</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2817</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3292</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1082</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>448; 4557</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2740</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1099; 6220</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2432</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7703</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15695</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10273</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4320</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>11604</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>25968</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5058</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2348</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4458; 11469</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10831; 21013</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3414</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4733</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1288; 7901</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6203; 15136</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2035; 8757</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3679</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>7151; 17088</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>19475; 33242</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2096; 9278</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>713; 5608</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4912</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10508</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4093</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1478; 6543</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1426; 5539</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3530; 9896</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>609; 4573</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2173; 8258</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6479; 14870</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>608; 4570</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9737</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20980</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2291</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>17189</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>39538</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5896; 14142</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15090; 26797</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3583</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>652; 6040</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3867; 12335</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13112; 25075</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3301; 11436</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3557</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>11547; 23800</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>31581; 48464</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3650; 11910</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>781; 7278</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$nada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Estudios-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,48</t>
+          <t>0,0; 65,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,23</t>
+          <t>0,0; 82,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 36,22</t>
+          <t>3,6; 36,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,41</t>
+          <t>0,0; 40,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,6; 37,38</t>
+          <t>6,41; 38,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,18; 54,49</t>
+          <t>21,63; 54,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,54; 55,37</t>
+          <t>28,19; 54,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,69</t>
+          <t>0,0; 21,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,95</t>
+          <t>0,0; 43,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 21,4</t>
+          <t>4,79; 20,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,82; 33,72</t>
+          <t>13,52; 35,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 27,9</t>
+          <t>6,16; 26,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,95</t>
+          <t>0,0; 25,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,34; 29,48</t>
+          <t>12,87; 29,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,51; 40,13</t>
+          <t>23,36; 39,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 19,37</t>
+          <t>4,89; 20,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 21,77</t>
+          <t>2,63; 21,83</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,35</t>
+          <t>0,0; 40,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,23; 67,39</t>
+          <t>15,2; 66,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,09; 81,89</t>
+          <t>21,25; 81,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,2; 62,24</t>
+          <t>20,8; 61,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,94; 67,2</t>
+          <t>9,09; 60,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,85; 48,84</t>
+          <t>13,39; 50,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,3; 58,07</t>
+          <t>26,38; 56,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 40,74</t>
+          <t>5,5; 42,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,7; 40,06</t>
+          <t>16,38; 41,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,18; 51,82</t>
+          <t>29,94; 53,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>0,0; 17,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 35,21</t>
+          <t>3,94; 33,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,31; 26,51</t>
+          <t>8,76; 26,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,87; 34,17</t>
+          <t>18,1; 34,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 28,08</t>
+          <t>7,52; 26,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,8</t>
+          <t>0,0; 12,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,11; 29,08</t>
+          <t>14,35; 28,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,25; 38,74</t>
+          <t>25,15; 38,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 18,58</t>
+          <t>5,82; 18,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 17,67</t>
+          <t>2,01; 15,96</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2817</t>
+          <t>0; 2713</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3292</t>
+          <t>0; 3333</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>448; 4557</t>
+          <t>453; 4616</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2740</t>
+          <t>0; 2839</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1099; 6220</t>
+          <t>1067; 6439</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4458; 11469</t>
+          <t>4551; 11513</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10831; 21013</t>
+          <t>10699; 20827</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3414</t>
+          <t>0; 3554</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4733</t>
+          <t>0; 4743</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1288; 7901</t>
+          <t>1770; 7655</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6203; 15136</t>
+          <t>6071; 15715</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2035; 8757</t>
+          <t>1933; 8402</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3679</t>
+          <t>0; 3788</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7151; 17088</t>
+          <t>7458; 16943</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19475; 33242</t>
+          <t>19353; 33078</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2096; 9278</t>
+          <t>2343; 9777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>713; 5608</t>
+          <t>678; 5625</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4093</t>
+          <t>0; 4146</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1478; 6543</t>
+          <t>1476; 6434</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1940,17 +1940,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1426; 5539</t>
+          <t>1438; 5504</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3530; 9896</t>
+          <t>3307; 9843</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>609; 4573</t>
+          <t>619; 4140</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1960,17 +1960,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2173; 8258</t>
+          <t>2265; 8482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6479; 14870</t>
+          <t>6754; 14492</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>608; 4570</t>
+          <t>617; 4794</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5896; 14142</t>
+          <t>5782; 14713</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15090; 26797</t>
+          <t>15485; 27624</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3583</t>
+          <t>0; 4185</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>652; 6040</t>
+          <t>676; 5804</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3867; 12335</t>
+          <t>4075; 12342</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13112; 25075</t>
+          <t>13283; 24956</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3301; 11436</t>
+          <t>3063; 10637</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3557</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11547; 23800</t>
+          <t>11747; 23448</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31581; 48464</t>
+          <t>31462; 48005</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3650; 11910</t>
+          <t>3729; 11888</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>781; 7278</t>
+          <t>829; 6574</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$nada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>16,38%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>31,22%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>60,26%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>67,19%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18,4%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18,4%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,24</t>
+          <t>3,62; 38,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 65,37</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 81,85</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 40,15</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6,81; 38,19</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,6; 36,69</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 40,83</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6,41; 38,7</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 80,38</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>36,6%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>41,36%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,47%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,63; 54,7</t>
+          <t>4,24; 20,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,19; 54,88</t>
+          <t>13,8; 34,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,54</t>
+          <t>4,76; 26,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,04</t>
+          <t>0,0; 22,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 20,73</t>
+          <t>21,47; 55,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,52; 35,0</t>
+          <t>29,19; 53,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 26,77</t>
+          <t>0,0; 22,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,69</t>
+          <t>0,0; 42,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,87; 29,23</t>
+          <t>12,68; 29,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,36; 39,93</t>
+          <t>23,4; 40,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 20,42</t>
+          <t>4,56; 19,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 21,83</t>
+          <t>2,83; 25,49</t>
         </is>
       </c>
     </row>
@@ -929,37 +929,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>52,5%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40,81%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29,23%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13,41%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>41,41%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>52,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -997,39 +997,39 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,88</t>
+          <t>21,23; 82,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 66,27</t>
+          <t>23,13; 61,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>8,95; 60,63</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 38,21</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19,17; 69,62</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>21,25; 81,38</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>20,8; 61,91</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,09; 60,84</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1037,17 +1037,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,39; 50,17</t>
+          <t>12,41; 47,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,38; 56,59</t>
+          <t>25,92; 57,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 42,73</t>
+          <t>0,0; 41,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,02%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25,29%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>27,58%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>40,57%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,38; 41,67</t>
+          <t>8,76; 25,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,94; 53,42</t>
+          <t>17,87; 34,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,91</t>
+          <t>7,45; 26,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 33,84</t>
+          <t>0,0; 13,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 26,53</t>
+          <t>17,2; 40,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,1; 34,01</t>
+          <t>29,63; 52,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 26,12</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,79</t>
+          <t>4,12; 33,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,35; 28,66</t>
+          <t>14,38; 28,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,15; 38,38</t>
+          <t>25,12; 38,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 18,55</t>
+          <t>6,19; 19,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 15,96</t>
+          <t>2,28; 17,29</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,62 +1436,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1265</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1797</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3062</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>756</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2713</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3333</t>
+          <t>455; 4829</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1519,47 +1519,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1082</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>0; 2690</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3317</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>453; 4616</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1125</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2792</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1133; 6354</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2839</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1067; 6439</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2432</t>
+          <t>0; 1821</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10273</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4320</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7703</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>15695</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1639</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3901</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10273</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4320</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2240</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4551; 11513</t>
+          <t>1564; 7736</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10699; 20827</t>
+          <t>6194; 15316</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3554</t>
+          <t>1495; 8284</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4743</t>
+          <t>0; 3070</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1770; 7655</t>
+          <t>4519; 11582</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6071; 15715</t>
+          <t>11079; 20479</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1933; 8402</t>
+          <t>0; 3737</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3788</t>
+          <t>0; 4672</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7458; 16943</t>
+          <t>7349; 17276</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19353; 33078</t>
+          <t>19385; 33371</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2343; 9777</t>
+          <t>2185; 9268</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>678; 5625</t>
+          <t>699; 6302</t>
         </is>
       </c>
     </row>
@@ -1784,37 +1784,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1852,37 +1852,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4020</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3551</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1920,39 +1920,39 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4146</t>
+          <t>1436; 5549</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1476; 6434</t>
+          <t>3678; 9722</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>609; 4126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3876</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1861; 6758</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1438; 5504</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3307; 9843</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>619; 4140</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1960,17 +1960,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2265; 8482</t>
+          <t>2099; 8059</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6754; 14492</t>
+          <t>6636; 14800</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>617; 4794</t>
+          <t>0; 4701</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>9737</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>20980</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2291</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7452</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18558</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6309</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2996</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5782; 14713</t>
+          <t>4075; 11831</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15485; 27624</t>
+          <t>13114; 25322</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>3033; 10746</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>676; 5804</t>
+          <t>0; 2912</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4075; 12342</t>
+          <t>6071; 14275</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13283; 24956</t>
+          <t>15323; 27200</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3063; 10637</t>
+          <t>0; 3632</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3074</t>
+          <t>707; 5701</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11747; 23448</t>
+          <t>11767; 23199</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31462; 48005</t>
+          <t>31420; 47721</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3729; 11888</t>
+          <t>3964; 12439</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>829; 6574</t>
+          <t>900; 6818</t>
         </is>
       </c>
     </row>
